--- a/artfynd/A 62008-2023 artfynd.xlsx
+++ b/artfynd/A 62008-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 62008-2023 artfynd.xlsx
+++ b/artfynd/A 62008-2023 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>113689193</v>
       </c>
       <c r="B2" t="n">
-        <v>57414</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,15 +784,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113689202</v>
+        <v>113689190</v>
       </c>
       <c r="B3" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -824,7 +814,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>90</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -841,10 +831,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>563478</v>
+        <v>563559</v>
       </c>
       <c r="R3" t="n">
-        <v>6418524</v>
+        <v>6418573</v>
       </c>
       <c r="S3" t="n">
         <v>75</v>
@@ -881,7 +871,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>2 lokaler på nordsidan av mindre kant</t>
+          <t>9 lokaler omfattande ca 90 ex. Pga teknikstrul tyvärr inte exakta koordinater, men flest där det började slutta mot N-NO.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -909,15 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113689190</v>
+        <v>113689202</v>
       </c>
       <c r="B4" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -944,7 +929,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -961,10 +946,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>563559</v>
+        <v>563478</v>
       </c>
       <c r="R4" t="n">
-        <v>6418573</v>
+        <v>6418524</v>
       </c>
       <c r="S4" t="n">
         <v>75</v>
@@ -1001,7 +986,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>9 lokaler omfattande ca 90 ex. Pga teknikstrul tyvärr inte exakta koordinater, men flest där det började slutta mot N-NO.</t>
+          <t>2 lokaler på nordsidan av mindre kant</t>
         </is>
       </c>
       <c r="AD4" t="b">
